--- a/Server/Received_data/Statistics/2024/Documents/Исходные данные без выбросов за 2024 год.xlsx
+++ b/Server/Received_data/Statistics/2024/Documents/Исходные данные без выбросов за 2024 год.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q162"/>
+  <dimension ref="A1:Q160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8477,66 +8477,66 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Lg</t>
+          <t>Peat</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lst</t>
+          <t>PFA</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LST-Syas-2024</t>
+          <t>PFA-Sk3-00-2024</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>8.567</v>
+        <v>4.12</v>
       </c>
       <c r="F137" t="n">
-        <v>0.71</v>
+        <v>0.4921</v>
       </c>
       <c r="G137" t="n">
-        <v>0.01031</v>
+        <v>0.01813</v>
       </c>
       <c r="H137" t="n">
-        <v>7.879</v>
+        <v>20.37</v>
       </c>
       <c r="I137" t="n">
-        <v>9.010999999999999</v>
+        <v>2.416</v>
       </c>
       <c r="J137" t="n">
-        <v>8.718999999999999</v>
+        <v>3.456</v>
       </c>
       <c r="K137" t="n">
-        <v>3.348</v>
+        <v>0.3283</v>
       </c>
       <c r="L137" t="n">
-        <v>2.099</v>
+        <v>1.163</v>
       </c>
       <c r="M137" t="n">
-        <v>4.842</v>
+        <v>39.39</v>
       </c>
       <c r="N137" t="n">
-        <v>0.06468</v>
+        <v>0.02127</v>
       </c>
       <c r="O137" t="n">
-        <v>0.06106</v>
+        <v>0.798</v>
       </c>
       <c r="P137" t="n">
-        <v>0.05925</v>
+        <v>0.03787</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.04836</v>
+        <v>0.5018</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -8550,52 +8550,52 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PFA-Sk3-00-2024</t>
+          <t>PFA-T1098-2024</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4.12</v>
+        <v>3.984</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4921</v>
+        <v>0.5406</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01813</v>
+        <v>0.0194</v>
       </c>
       <c r="H138" t="n">
-        <v>20.37</v>
+        <v>24.7</v>
       </c>
       <c r="I138" t="n">
-        <v>2.416</v>
+        <v>2.189</v>
       </c>
       <c r="J138" t="n">
-        <v>3.456</v>
+        <v>3.422</v>
       </c>
       <c r="K138" t="n">
-        <v>0.3283</v>
+        <v>0.3552</v>
       </c>
       <c r="L138" t="n">
-        <v>1.163</v>
+        <v>1.104</v>
       </c>
       <c r="M138" t="n">
-        <v>39.39</v>
+        <v>47.43</v>
       </c>
       <c r="N138" t="n">
-        <v>0.02127</v>
+        <v>0.02917</v>
       </c>
       <c r="O138" t="n">
-        <v>0.798</v>
+        <v>1</v>
       </c>
       <c r="P138" t="n">
-        <v>0.03787</v>
+        <v>0.04987</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.5018</v>
+        <v>0.5279</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -8609,52 +8609,52 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>PFA-T1098-2024</t>
+          <t>PFA-T598-2024</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3.984</v>
+        <v>3.862</v>
       </c>
       <c r="F139" t="n">
-        <v>0.5406</v>
+        <v>0.4807</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0194</v>
+        <v>0.02112</v>
       </c>
       <c r="H139" t="n">
-        <v>24.7</v>
+        <v>21.18</v>
       </c>
       <c r="I139" t="n">
-        <v>2.189</v>
+        <v>2.27</v>
       </c>
       <c r="J139" t="n">
-        <v>3.422</v>
+        <v>3.326</v>
       </c>
       <c r="K139" t="n">
-        <v>0.3552</v>
+        <v>0.5</v>
       </c>
       <c r="L139" t="n">
-        <v>1.104</v>
+        <v>1.103</v>
       </c>
       <c r="M139" t="n">
-        <v>47.43</v>
+        <v>23.19</v>
       </c>
       <c r="N139" t="n">
-        <v>0.02917</v>
+        <v>0.01905</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="P139" t="n">
-        <v>0.04987</v>
+        <v>0.03697</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.5279</v>
+        <v>0.3899</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -8668,52 +8668,52 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>PFA-T598-2024</t>
+          <t>PFA-T5H98-2024</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3.862</v>
+        <v>3.806</v>
       </c>
       <c r="F140" t="n">
-        <v>0.4807</v>
+        <v>0.3613</v>
       </c>
       <c r="G140" t="n">
-        <v>0.02112</v>
+        <v>0.01845</v>
       </c>
       <c r="H140" t="n">
-        <v>21.18</v>
+        <v>23.11</v>
       </c>
       <c r="I140" t="n">
-        <v>2.27</v>
+        <v>1.564</v>
       </c>
       <c r="J140" t="n">
-        <v>3.326</v>
+        <v>3.566</v>
       </c>
       <c r="K140" t="n">
-        <v>0.5</v>
+        <v>0.4333</v>
       </c>
       <c r="L140" t="n">
-        <v>1.103</v>
+        <v>1.176</v>
       </c>
       <c r="M140" t="n">
-        <v>23.19</v>
+        <v>39.53</v>
       </c>
       <c r="N140" t="n">
-        <v>0.01905</v>
+        <v>0.01463</v>
       </c>
       <c r="O140" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6773</v>
       </c>
       <c r="P140" t="n">
-        <v>0.03697</v>
+        <v>0.0362</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.3899</v>
+        <v>0.3447</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -8727,52 +8727,52 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>PFA-T5H98-2024</t>
+          <t>PFA-T698-2024</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3.806</v>
+        <v>3.612</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3613</v>
+        <v>0.4165</v>
       </c>
       <c r="G141" t="n">
-        <v>0.01845</v>
+        <v>0.02146</v>
       </c>
       <c r="H141" t="n">
-        <v>23.11</v>
+        <v>24.08</v>
       </c>
       <c r="I141" t="n">
-        <v>1.564</v>
+        <v>1.73</v>
       </c>
       <c r="J141" t="n">
-        <v>3.566</v>
+        <v>3.449</v>
       </c>
       <c r="K141" t="n">
-        <v>0.4333</v>
+        <v>0.4345</v>
       </c>
       <c r="L141" t="n">
-        <v>1.176</v>
+        <v>1.148</v>
       </c>
       <c r="M141" t="n">
-        <v>39.53</v>
+        <v>43.54</v>
       </c>
       <c r="N141" t="n">
-        <v>0.01463</v>
+        <v>0.01256</v>
       </c>
       <c r="O141" t="n">
-        <v>0.6773</v>
+        <v>0.5536</v>
       </c>
       <c r="P141" t="n">
-        <v>0.0362</v>
+        <v>0.03096</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.3447</v>
+        <v>0.3059</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -8781,57 +8781,57 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PFA</t>
+          <t>PHA</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>PFA-T698-2024</t>
+          <t>PHA-Sk3-00-2024</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3.612</v>
+        <v>2.921</v>
       </c>
       <c r="F142" t="n">
-        <v>0.4165</v>
+        <v>0.2902</v>
       </c>
       <c r="G142" t="n">
-        <v>0.02146</v>
+        <v>0.02443</v>
       </c>
       <c r="H142" t="n">
-        <v>24.08</v>
+        <v>20.37</v>
       </c>
       <c r="I142" t="n">
-        <v>1.73</v>
+        <v>1.425</v>
       </c>
       <c r="J142" t="n">
-        <v>3.449</v>
+        <v>2.398</v>
       </c>
       <c r="K142" t="n">
-        <v>0.4345</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="L142" t="n">
-        <v>1.148</v>
+        <v>1.036</v>
       </c>
       <c r="M142" t="n">
-        <v>43.54</v>
+        <v>14.04</v>
       </c>
       <c r="N142" t="n">
-        <v>0.01256</v>
+        <v>0.008383</v>
       </c>
       <c r="O142" t="n">
-        <v>0.5536</v>
+        <v>0.1423</v>
       </c>
       <c r="P142" t="n">
-        <v>0.03096</v>
+        <v>0.01393</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.3059</v>
+        <v>0.1763</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -8845,52 +8845,52 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>PHA-Sk3-00-2024</t>
+          <t>PHA-T598-2024</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2.921</v>
+        <v>2.633</v>
       </c>
       <c r="F143" t="n">
-        <v>0.2902</v>
+        <v>0.6589</v>
       </c>
       <c r="G143" t="n">
-        <v>0.02443</v>
+        <v>0.06308</v>
       </c>
       <c r="H143" t="n">
-        <v>20.37</v>
+        <v>17.8</v>
       </c>
       <c r="I143" t="n">
-        <v>1.425</v>
+        <v>3.702</v>
       </c>
       <c r="J143" t="n">
-        <v>2.398</v>
+        <v>2.017</v>
       </c>
       <c r="K143" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.8227</v>
       </c>
       <c r="L143" t="n">
-        <v>1.036</v>
+        <v>1.016</v>
       </c>
       <c r="M143" t="n">
-        <v>14.04</v>
+        <v>6.519</v>
       </c>
       <c r="N143" t="n">
-        <v>0.008383</v>
+        <v>0.01172</v>
       </c>
       <c r="O143" t="n">
-        <v>0.1423</v>
+        <v>0.08062</v>
       </c>
       <c r="P143" t="n">
-        <v>0.01393</v>
+        <v>0.01381</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.1763</v>
+        <v>0.1564</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -8904,52 +8904,52 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>PHA-T598-2024</t>
+          <t>PHA-T698-2024</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2.633</v>
+        <v>2.437</v>
       </c>
       <c r="F144" t="n">
-        <v>0.6589</v>
+        <v>0.6341</v>
       </c>
       <c r="G144" t="n">
-        <v>0.06308</v>
+        <v>0.07134</v>
       </c>
       <c r="H144" t="n">
-        <v>17.8</v>
+        <v>22.43</v>
       </c>
       <c r="I144" t="n">
-        <v>3.702</v>
+        <v>2.827</v>
       </c>
       <c r="J144" t="n">
-        <v>2.017</v>
+        <v>1.737</v>
       </c>
       <c r="K144" t="n">
-        <v>0.8227</v>
+        <v>0.7543</v>
       </c>
       <c r="L144" t="n">
-        <v>1.016</v>
+        <v>0.9704</v>
       </c>
       <c r="M144" t="n">
-        <v>6.519</v>
+        <v>8.807</v>
       </c>
       <c r="N144" t="n">
-        <v>0.01172</v>
+        <v>0.01102</v>
       </c>
       <c r="O144" t="n">
-        <v>0.08062</v>
+        <v>0.0664</v>
       </c>
       <c r="P144" t="n">
-        <v>0.01381</v>
+        <v>0.02074</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.1564</v>
+        <v>0.1498</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -8963,52 +8963,52 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>PHA-T698-2024</t>
+          <t>PHA-TTL98-2024</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2.437</v>
+        <v>2.655</v>
       </c>
       <c r="F145" t="n">
-        <v>0.6341</v>
+        <v>0.7224</v>
       </c>
       <c r="G145" t="n">
-        <v>0.07134</v>
+        <v>0.06916</v>
       </c>
       <c r="H145" t="n">
-        <v>22.43</v>
+        <v>18.37</v>
       </c>
       <c r="I145" t="n">
-        <v>2.827</v>
+        <v>3.932</v>
       </c>
       <c r="J145" t="n">
-        <v>1.737</v>
+        <v>2.009</v>
       </c>
       <c r="K145" t="n">
-        <v>0.7543</v>
+        <v>0.681</v>
       </c>
       <c r="L145" t="n">
-        <v>0.9704</v>
+        <v>0.9859</v>
       </c>
       <c r="M145" t="n">
-        <v>8.807</v>
+        <v>10.83</v>
       </c>
       <c r="N145" t="n">
-        <v>0.01102</v>
+        <v>0.01211</v>
       </c>
       <c r="O145" t="n">
-        <v>0.0664</v>
+        <v>0.1012</v>
       </c>
       <c r="P145" t="n">
-        <v>0.02074</v>
+        <v>0.02291</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.1498</v>
+        <v>0.1834</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -9017,57 +9017,57 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PHA</t>
+          <t>PHF</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>PHA-TTL98-2024</t>
+          <t>PHF-Sk300-2024</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2.655</v>
+        <v>2.988</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7224</v>
+        <v>0.8065</v>
       </c>
       <c r="G146" t="n">
-        <v>0.06916</v>
+        <v>0.06529</v>
       </c>
       <c r="H146" t="n">
-        <v>18.37</v>
+        <v>17.29</v>
       </c>
       <c r="I146" t="n">
-        <v>3.932</v>
+        <v>4.665</v>
       </c>
       <c r="J146" t="n">
-        <v>2.009</v>
+        <v>2.161</v>
       </c>
       <c r="K146" t="n">
-        <v>0.681</v>
+        <v>0.3623</v>
       </c>
       <c r="L146" t="n">
-        <v>0.9859</v>
+        <v>1.002</v>
       </c>
       <c r="M146" t="n">
-        <v>10.83</v>
+        <v>14.89</v>
       </c>
       <c r="N146" t="n">
-        <v>0.01211</v>
+        <v>0.01136</v>
       </c>
       <c r="O146" t="n">
-        <v>0.1012</v>
+        <v>0.2497</v>
       </c>
       <c r="P146" t="n">
-        <v>0.02291</v>
+        <v>0.01749</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.1834</v>
+        <v>0.3162</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -9081,52 +9081,52 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>PHF-Sk300-2024</t>
+          <t>PHF-T10L98-2024</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2.988</v>
+        <v>3.044</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8065</v>
+        <v>0.4048</v>
       </c>
       <c r="G147" t="n">
-        <v>0.06529</v>
+        <v>0.03023</v>
       </c>
       <c r="H147" t="n">
-        <v>17.29</v>
+        <v>16.62</v>
       </c>
       <c r="I147" t="n">
-        <v>4.665</v>
+        <v>2.436</v>
       </c>
       <c r="J147" t="n">
-        <v>2.161</v>
+        <v>2.417</v>
       </c>
       <c r="K147" t="n">
-        <v>0.3623</v>
+        <v>0.4001</v>
       </c>
       <c r="L147" t="n">
-        <v>1.002</v>
+        <v>1.018</v>
       </c>
       <c r="M147" t="n">
-        <v>14.89</v>
+        <v>19.65</v>
       </c>
       <c r="N147" t="n">
-        <v>0.01136</v>
+        <v>0.008867999999999999</v>
       </c>
       <c r="O147" t="n">
-        <v>0.2497</v>
+        <v>0.1954</v>
       </c>
       <c r="P147" t="n">
-        <v>0.01749</v>
+        <v>0.0164</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.3162</v>
+        <v>0.2005</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -9140,52 +9140,52 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>PHF-T10L98-2024</t>
+          <t>PHF-T698-2024</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3.044</v>
+        <v>2.64</v>
       </c>
       <c r="F148" t="n">
-        <v>0.4048</v>
+        <v>0.5448</v>
       </c>
       <c r="G148" t="n">
-        <v>0.03023</v>
+        <v>0.05425</v>
       </c>
       <c r="H148" t="n">
-        <v>16.62</v>
+        <v>15.6</v>
       </c>
       <c r="I148" t="n">
-        <v>2.436</v>
+        <v>3.493</v>
       </c>
       <c r="J148" t="n">
-        <v>2.417</v>
+        <v>2.429</v>
       </c>
       <c r="K148" t="n">
-        <v>0.4001</v>
+        <v>0.5766</v>
       </c>
       <c r="L148" t="n">
-        <v>1.018</v>
+        <v>1.084</v>
       </c>
       <c r="M148" t="n">
-        <v>19.65</v>
+        <v>15.2</v>
       </c>
       <c r="N148" t="n">
-        <v>0.008867999999999999</v>
+        <v>0.006822</v>
       </c>
       <c r="O148" t="n">
-        <v>0.1954</v>
+        <v>0.1216</v>
       </c>
       <c r="P148" t="n">
-        <v>0.0164</v>
+        <v>0.01349</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.2005</v>
+        <v>0.1262</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -9199,52 +9199,52 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>PHF-T698-2024</t>
+          <t>PHF-T7H98-2024</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5448</v>
+        <v>0.55</v>
       </c>
       <c r="G149" t="n">
-        <v>0.05425</v>
+        <v>0.05064</v>
       </c>
       <c r="H149" t="n">
-        <v>15.6</v>
+        <v>14.55</v>
       </c>
       <c r="I149" t="n">
-        <v>3.493</v>
+        <v>3.78</v>
       </c>
       <c r="J149" t="n">
-        <v>2.429</v>
+        <v>2.66</v>
       </c>
       <c r="K149" t="n">
-        <v>0.5766</v>
+        <v>0.5457</v>
       </c>
       <c r="L149" t="n">
-        <v>1.084</v>
+        <v>1.101</v>
       </c>
       <c r="M149" t="n">
-        <v>15.2</v>
+        <v>14.81</v>
       </c>
       <c r="N149" t="n">
-        <v>0.006822</v>
+        <v>0.01158</v>
       </c>
       <c r="O149" t="n">
-        <v>0.1216</v>
+        <v>0.1739</v>
       </c>
       <c r="P149" t="n">
-        <v>0.01349</v>
+        <v>0.01575</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.1262</v>
+        <v>0.1782</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -9258,111 +9258,111 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>PHF-T7H98-2024</t>
+          <t>PHF-TTL98-2024</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2.76</v>
+        <v>2.695</v>
       </c>
       <c r="F150" t="n">
-        <v>0.55</v>
+        <v>0.6227</v>
       </c>
       <c r="G150" t="n">
-        <v>0.05064</v>
+        <v>0.0563</v>
       </c>
       <c r="H150" t="n">
-        <v>14.55</v>
+        <v>15.48</v>
       </c>
       <c r="I150" t="n">
-        <v>3.78</v>
+        <v>4.023</v>
       </c>
       <c r="J150" t="n">
-        <v>2.66</v>
+        <v>2.364</v>
       </c>
       <c r="K150" t="n">
-        <v>0.5457</v>
+        <v>0.3496</v>
       </c>
       <c r="L150" t="n">
-        <v>1.101</v>
+        <v>1.018</v>
       </c>
       <c r="M150" t="n">
-        <v>14.81</v>
+        <v>22.64</v>
       </c>
       <c r="N150" t="n">
-        <v>0.01158</v>
+        <v>0.007385</v>
       </c>
       <c r="O150" t="n">
-        <v>0.1739</v>
+        <v>0.2126</v>
       </c>
       <c r="P150" t="n">
-        <v>0.01575</v>
+        <v>0.01448</v>
       </c>
       <c r="Q150" t="n">
-        <v>0.1782</v>
+        <v>0.2255</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Peat</t>
+          <t>Soil</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PHF</t>
+          <t>SFA</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>PHF-TTL98-2024</t>
+          <t>SFA-PW04-2024</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2.695</v>
+        <v>3.653</v>
       </c>
       <c r="F151" t="n">
-        <v>0.6227</v>
+        <v>0.3846</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0563</v>
+        <v>0.01954</v>
       </c>
       <c r="H151" t="n">
-        <v>15.48</v>
+        <v>23.13</v>
       </c>
       <c r="I151" t="n">
-        <v>4.023</v>
+        <v>1.663</v>
       </c>
       <c r="J151" t="n">
-        <v>2.364</v>
+        <v>2.694</v>
       </c>
       <c r="K151" t="n">
-        <v>0.3496</v>
+        <v>0.3183</v>
       </c>
       <c r="L151" t="n">
-        <v>1.018</v>
+        <v>0.9565</v>
       </c>
       <c r="M151" t="n">
-        <v>22.64</v>
+        <v>46.24</v>
       </c>
       <c r="N151" t="n">
-        <v>0.007385</v>
+        <v>0.0162</v>
       </c>
       <c r="O151" t="n">
-        <v>0.2126</v>
+        <v>0.4161</v>
       </c>
       <c r="P151" t="n">
-        <v>0.01448</v>
+        <v>0.0236</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.2255</v>
+        <v>0.4105</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -9376,52 +9376,52 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SFA-PW04-2024</t>
+          <t>SFA-PW16-2024</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3.653</v>
+        <v>4.404</v>
       </c>
       <c r="F152" t="n">
-        <v>0.3846</v>
+        <v>0.5484</v>
       </c>
       <c r="G152" t="n">
-        <v>0.01954</v>
+        <v>0.01638</v>
       </c>
       <c r="H152" t="n">
-        <v>23.13</v>
+        <v>18.49</v>
       </c>
       <c r="I152" t="n">
-        <v>1.663</v>
+        <v>2.966</v>
       </c>
       <c r="J152" t="n">
-        <v>2.694</v>
+        <v>3.266</v>
       </c>
       <c r="K152" t="n">
-        <v>0.3183</v>
+        <v>0.4615</v>
       </c>
       <c r="L152" t="n">
-        <v>0.9565</v>
+        <v>1.076</v>
       </c>
       <c r="M152" t="n">
-        <v>46.24</v>
+        <v>18.5</v>
       </c>
       <c r="N152" t="n">
-        <v>0.0162</v>
+        <v>0.02546</v>
       </c>
       <c r="O152" t="n">
-        <v>0.4161</v>
+        <v>0.6829</v>
       </c>
       <c r="P152" t="n">
-        <v>0.0236</v>
+        <v>0.03856</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.4105</v>
+        <v>0.5037</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -9430,57 +9430,57 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SFA</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SFA-PW16-2024</t>
+          <t>SHA-CtK04-2024</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4.404</v>
+        <v>2.329</v>
       </c>
       <c r="F153" t="n">
-        <v>0.5484</v>
+        <v>0.5261</v>
       </c>
       <c r="G153" t="n">
-        <v>0.01638</v>
+        <v>0.07627</v>
       </c>
       <c r="H153" t="n">
-        <v>18.49</v>
+        <v>12.29</v>
       </c>
       <c r="I153" t="n">
-        <v>2.966</v>
+        <v>4.281</v>
       </c>
       <c r="J153" t="n">
-        <v>3.266</v>
+        <v>1.279</v>
       </c>
       <c r="K153" t="n">
-        <v>0.4615</v>
+        <v>0.3227</v>
       </c>
       <c r="L153" t="n">
-        <v>1.076</v>
+        <v>0.8927</v>
       </c>
       <c r="M153" t="n">
-        <v>18.5</v>
+        <v>17.61</v>
       </c>
       <c r="N153" t="n">
-        <v>0.02546</v>
+        <v>0.007764</v>
       </c>
       <c r="O153" t="n">
-        <v>0.6829</v>
+        <v>0.1515</v>
       </c>
       <c r="P153" t="n">
-        <v>0.03856</v>
+        <v>0.01517</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.5037</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -9494,52 +9494,52 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SHA-CtK04-2024</t>
+          <t>SHA-CtV98-2024</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2.329</v>
+        <v>2.197</v>
       </c>
       <c r="F154" t="n">
-        <v>0.5261</v>
+        <v>0.2273</v>
       </c>
       <c r="G154" t="n">
-        <v>0.07627</v>
+        <v>0.03995</v>
       </c>
       <c r="H154" t="n">
-        <v>12.29</v>
+        <v>7.86</v>
       </c>
       <c r="I154" t="n">
-        <v>4.281</v>
+        <v>2.891</v>
       </c>
       <c r="J154" t="n">
-        <v>1.279</v>
+        <v>1.101</v>
       </c>
       <c r="K154" t="n">
-        <v>0.3227</v>
+        <v>0.3604</v>
       </c>
       <c r="L154" t="n">
-        <v>0.8927</v>
+        <v>0.887</v>
       </c>
       <c r="M154" t="n">
-        <v>17.61</v>
+        <v>16.07</v>
       </c>
       <c r="N154" t="n">
-        <v>0.007764</v>
+        <v>0.01096</v>
       </c>
       <c r="O154" t="n">
-        <v>0.1515</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="P154" t="n">
-        <v>0.01517</v>
+        <v>0.02207</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.3674</v>
+        <v>0.3621</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -9553,52 +9553,52 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SHA-CtK15-2024</t>
+          <t>SHA-PW04-2024</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2.19</v>
+        <v>2.713</v>
       </c>
       <c r="F155" t="n">
-        <v>1.206</v>
+        <v>0.1459</v>
       </c>
       <c r="G155" t="n">
-        <v>0.1874</v>
+        <v>0.01501</v>
       </c>
       <c r="H155" t="n">
-        <v>20.43</v>
+        <v>5.504</v>
       </c>
       <c r="I155" t="n">
-        <v>5.904</v>
+        <v>2.652</v>
       </c>
       <c r="J155" t="n">
-        <v>0.9705</v>
+        <v>2.166</v>
       </c>
       <c r="K155" t="n">
-        <v>0.1514</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="L155" t="n">
-        <v>0.8298</v>
+        <v>1.045</v>
       </c>
       <c r="M155" t="n">
-        <v>39.65</v>
+        <v>7.659</v>
       </c>
       <c r="N155" t="n">
-        <v>0.00219</v>
+        <v>0.005618</v>
       </c>
       <c r="O155" t="n">
-        <v>0.251</v>
+        <v>0.03432</v>
       </c>
       <c r="P155" t="n">
-        <v>0.01486</v>
+        <v>0.009009</v>
       </c>
       <c r="Q155" t="n">
-        <v>0.8178</v>
+        <v>0.07371</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -9612,52 +9612,52 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>SHA-CtV98-2024</t>
+          <t>SHA-PW16-2024</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2.197</v>
+        <v>2.94</v>
       </c>
       <c r="F156" t="n">
-        <v>0.2273</v>
+        <v>0.6297</v>
       </c>
       <c r="G156" t="n">
-        <v>0.03995</v>
+        <v>0.07641000000000001</v>
       </c>
       <c r="H156" t="n">
-        <v>7.86</v>
+        <v>14.88</v>
       </c>
       <c r="I156" t="n">
-        <v>2.891</v>
+        <v>4.232</v>
       </c>
       <c r="J156" t="n">
-        <v>1.101</v>
+        <v>1.176</v>
       </c>
       <c r="K156" t="n">
-        <v>0.3604</v>
+        <v>0.2275</v>
       </c>
       <c r="L156" t="n">
-        <v>0.887</v>
+        <v>0.6784</v>
       </c>
       <c r="M156" t="n">
-        <v>16.07</v>
+        <v>26.42</v>
       </c>
       <c r="N156" t="n">
-        <v>0.01096</v>
+        <v>0.009627</v>
       </c>
       <c r="O156" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.2184</v>
       </c>
       <c r="P156" t="n">
-        <v>0.02207</v>
+        <v>0.0224</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.3621</v>
+        <v>0.7187</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -9666,57 +9666,57 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>SHF</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SHA-PW04-2024</t>
+          <t>SHF-CmK98-2024</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2.713</v>
+        <v>2.178</v>
       </c>
       <c r="F157" t="n">
-        <v>0.1459</v>
+        <v>0.1829</v>
       </c>
       <c r="G157" t="n">
-        <v>0.01501</v>
+        <v>0.03157</v>
       </c>
       <c r="H157" t="n">
-        <v>5.504</v>
+        <v>3.479</v>
       </c>
       <c r="I157" t="n">
-        <v>2.652</v>
+        <v>5.258</v>
       </c>
       <c r="J157" t="n">
-        <v>2.166</v>
+        <v>1.335</v>
       </c>
       <c r="K157" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.2486</v>
       </c>
       <c r="L157" t="n">
-        <v>1.045</v>
+        <v>0.9616</v>
       </c>
       <c r="M157" t="n">
-        <v>7.659</v>
+        <v>29.92</v>
       </c>
       <c r="N157" t="n">
-        <v>0.005618</v>
+        <v>0.006766</v>
       </c>
       <c r="O157" t="n">
-        <v>0.03432</v>
+        <v>0.1258</v>
       </c>
       <c r="P157" t="n">
-        <v>0.009009</v>
+        <v>0.0112</v>
       </c>
       <c r="Q157" t="n">
-        <v>0.07371</v>
+        <v>0.2692</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -9725,57 +9725,57 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>SHF</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SHA-PW16-2024</t>
+          <t>SHF-CtL00-2024</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2.94</v>
+        <v>2.991</v>
       </c>
       <c r="F158" t="n">
-        <v>0.6297</v>
+        <v>0.3581</v>
       </c>
       <c r="G158" t="n">
-        <v>0.07641000000000001</v>
+        <v>0.03917</v>
       </c>
       <c r="H158" t="n">
-        <v>14.88</v>
+        <v>13.96</v>
       </c>
       <c r="I158" t="n">
-        <v>4.232</v>
+        <v>2.565</v>
       </c>
       <c r="J158" t="n">
-        <v>1.176</v>
+        <v>1.569</v>
       </c>
       <c r="K158" t="n">
-        <v>0.2275</v>
+        <v>0.3806</v>
       </c>
       <c r="L158" t="n">
-        <v>0.6784</v>
+        <v>0.88</v>
       </c>
       <c r="M158" t="n">
-        <v>26.42</v>
+        <v>18.7</v>
       </c>
       <c r="N158" t="n">
-        <v>0.009627</v>
+        <v>0.008279</v>
       </c>
       <c r="O158" t="n">
-        <v>0.2184</v>
+        <v>0.1107</v>
       </c>
       <c r="P158" t="n">
-        <v>0.0224</v>
+        <v>0.01401</v>
       </c>
       <c r="Q158" t="n">
-        <v>0.7187</v>
+        <v>0.2328</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -9789,52 +9789,52 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SHF-CmK98-2024</t>
+          <t>SHF-Ctv98-2024</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2.178</v>
+        <v>2.198</v>
       </c>
       <c r="F159" t="n">
-        <v>0.1829</v>
+        <v>0.3225</v>
       </c>
       <c r="G159" t="n">
-        <v>0.03157</v>
+        <v>0.05493</v>
       </c>
       <c r="H159" t="n">
-        <v>3.479</v>
+        <v>15.99</v>
       </c>
       <c r="I159" t="n">
-        <v>5.258</v>
+        <v>2.017</v>
       </c>
       <c r="J159" t="n">
-        <v>1.335</v>
+        <v>1.237</v>
       </c>
       <c r="K159" t="n">
-        <v>0.2486</v>
+        <v>0.2039</v>
       </c>
       <c r="L159" t="n">
-        <v>0.9616</v>
+        <v>0.902</v>
       </c>
       <c r="M159" t="n">
-        <v>29.92</v>
+        <v>47.25</v>
       </c>
       <c r="N159" t="n">
-        <v>0.006766</v>
+        <v>0.005621</v>
       </c>
       <c r="O159" t="n">
-        <v>0.1258</v>
+        <v>0.1932</v>
       </c>
       <c r="P159" t="n">
-        <v>0.0112</v>
+        <v>0.01346</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.2692</v>
+        <v>0.4354</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -9848,164 +9848,46 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>SHF-CtL00-2024</t>
+          <t>SHF-PW04-2024</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2.991</v>
+        <v>3.382</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3581</v>
+        <v>0.2071</v>
       </c>
       <c r="G160" t="n">
-        <v>0.03917</v>
+        <v>0.01563</v>
       </c>
       <c r="H160" t="n">
-        <v>13.96</v>
+        <v>4.598</v>
       </c>
       <c r="I160" t="n">
-        <v>2.565</v>
+        <v>4.505</v>
       </c>
       <c r="J160" t="n">
-        <v>1.569</v>
+        <v>3.081</v>
       </c>
       <c r="K160" t="n">
-        <v>0.3806</v>
+        <v>0.3485</v>
       </c>
       <c r="L160" t="n">
-        <v>0.88</v>
+        <v>1.111</v>
       </c>
       <c r="M160" t="n">
-        <v>18.7</v>
+        <v>25.32</v>
       </c>
       <c r="N160" t="n">
-        <v>0.008279</v>
+        <v>0.007718</v>
       </c>
       <c r="O160" t="n">
-        <v>0.1107</v>
+        <v>0.2849</v>
       </c>
       <c r="P160" t="n">
-        <v>0.01401</v>
+        <v>0.01447</v>
       </c>
       <c r="Q160" t="n">
-        <v>0.2328</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="n">
-        <v>173</v>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Soil</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>SHF</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>SHF-Ctv98-2024</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>2.198</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0.3225</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0.05493</v>
-      </c>
-      <c r="H161" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="I161" t="n">
-        <v>2.017</v>
-      </c>
-      <c r="J161" t="n">
-        <v>1.237</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0.2039</v>
-      </c>
-      <c r="L161" t="n">
-        <v>0.902</v>
-      </c>
-      <c r="M161" t="n">
-        <v>47.25</v>
-      </c>
-      <c r="N161" t="n">
-        <v>0.005621</v>
-      </c>
-      <c r="O161" t="n">
-        <v>0.1932</v>
-      </c>
-      <c r="P161" t="n">
-        <v>0.01346</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0.4354</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="1" t="n">
-        <v>174</v>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Soil</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>SHF</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>SHF-PW04-2024</t>
-        </is>
-      </c>
-      <c r="E162" t="n">
-        <v>3.382</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0.2071</v>
-      </c>
-      <c r="G162" t="n">
-        <v>0.01563</v>
-      </c>
-      <c r="H162" t="n">
-        <v>4.598</v>
-      </c>
-      <c r="I162" t="n">
-        <v>4.505</v>
-      </c>
-      <c r="J162" t="n">
-        <v>3.081</v>
-      </c>
-      <c r="K162" t="n">
-        <v>0.3485</v>
-      </c>
-      <c r="L162" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="M162" t="n">
-        <v>25.32</v>
-      </c>
-      <c r="N162" t="n">
-        <v>0.007718</v>
-      </c>
-      <c r="O162" t="n">
-        <v>0.2849</v>
-      </c>
-      <c r="P162" t="n">
-        <v>0.01447</v>
-      </c>
-      <c r="Q162" t="n">
         <v>0.2081</v>
       </c>
     </row>
